--- a/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
@@ -323,7 +323,7 @@
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
@@ -408,27 +408,27 @@
     </comment>
     <comment ref="E17" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E20" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E22" authorId="0" shapeId="0">
@@ -453,12 +453,12 @@
     </comment>
     <comment ref="E26" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
@@ -468,7 +468,7 @@
     </comment>
     <comment ref="E29" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado: las 20 f... · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1055/2003, de 1 de agosto, por el que se aprueba la Reglamentación técnico-sanitaria sobre los productos de cacao y chocolate destinados a la alimentación humana (B... (La tabla de mínimos de los apartados 1.1 a 1.13 más 6.g) se ha cotejado fila a fila contra el consolidado:...) · https://www.boe.es/buscar/act.php?id=BOE-A-2003-15599</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -4582,8 +4582,8 @@
         </is>
       </c>
       <c r="N31" t="str">
-        <f>IF(M31="No","La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L31)),"",IF(L31&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
-        <v>La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
+        <f>IF(M31="No","La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L31)),"",IF(L31&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
+        <v>La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
@@ -4654,8 +4654,8 @@
         </is>
       </c>
       <c r="N32" t="str">
-        <f>IF(M32="No","La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L32)),"",IF(L32&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
-        <v>La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
+        <f>IF(M32="No","La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L32)),"",IF(L32&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
+        <v>La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
       </c>
       <c r="O32" s="13" t="inlineStr">
         <is>
@@ -4726,8 +4726,8 @@
         </is>
       </c>
       <c r="N33" t="str">
-        <f>IF(M33="No","La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L33)),"",IF(L33&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
-        <v>La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
+        <f>IF(M33="No","La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L33)),"",IF(L33&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
+        <v>La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
@@ -4798,8 +4798,8 @@
         </is>
       </c>
       <c r="N34" t="str">
-        <f>IF(M34="No","La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L34)),"",IF(L34&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
-        <v>La denominación va por pieza: el 25 %% lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
+        <f>IF(M34="No","La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja",IF(NOT(ISNUMBER(L34)),"",IF(L34&gt;=$B$38,"CUMPLE el 25 % sobre el peso total","NO CUMPLE: no puede llamarse así")))</f>
+        <v>La denominación va por pieza: el 25 % lo comprueba cada bombón en su propia fila, no el agregado de la caja</v>
       </c>
       <c r="O34" s="13" t="inlineStr">
         <is>
